--- a/data/programado.xlsx
+++ b/data/programado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE1290F-8198-4EBA-83C3-17C8E1DE627B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A424A858-F728-4BE2-BAE2-6B5FA911DE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1419,7 +1419,7 @@
   <dimension ref="A1:N204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.7109375" bestFit="1" customWidth="1"/>
